--- a/docentes/Urias Morales Alejandra - Estadisticos 20232.xlsx
+++ b/docentes/Urias Morales Alejandra - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
   </si>
 </sst>
 </file>
@@ -655,16 +646,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.95999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -678,16 +672,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -701,16 +698,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -724,16 +724,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H5">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -747,16 +750,19 @@
         <v>30</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>30</v>
       </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -812,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>82.61</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -847,7 +853,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -864,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -890,13 +896,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H5">
         <v>9.199999999999999</v>
@@ -925,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -965,29 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920363</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Urias Morales Alejandra - Estadisticos 20232.xlsx
+++ b/docentes/Urias Morales Alejandra - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -818,16 +827,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -844,16 +853,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>80.65000000000001</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,16 +879,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -905,7 +914,7 @@
         <v>96</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -931,7 +940,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -971,6 +980,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920356</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
